--- a/testdata/data - UAT.xlsx
+++ b/testdata/data - UAT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12240"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="89">
   <si>
     <t>username</t>
   </si>
@@ -167,6 +167,18 @@
     <t>domestic_payment_bban2</t>
   </si>
   <si>
+    <t>cards_item_debit_card_name</t>
+  </si>
+  <si>
+    <t>cards_item_debit_card_number</t>
+  </si>
+  <si>
+    <t>cards_item_credit_card_name</t>
+  </si>
+  <si>
+    <t>cards_item_credit_card_number</t>
+  </si>
+  <si>
     <t>mirko.lekic@ibank</t>
   </si>
   <si>
@@ -270,6 +282,18 @@
   </si>
   <si>
     <t>205-9001015647000-10</t>
+  </si>
+  <si>
+    <t>Master Debit Contactless - STOJKA PEŠIĆ</t>
+  </si>
+  <si>
+    <t>5169********5796</t>
+  </si>
+  <si>
+    <t>Visa PrePaid - STOJKA PEŠIĆ</t>
+  </si>
+  <si>
+    <t>4313********5309</t>
   </si>
 </sst>
 </file>
@@ -896,7 +920,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -910,6 +934,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1454,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="17.712962962963" style="3" customWidth="1"/>
@@ -1499,10 +1526,14 @@
     <col min="44" max="44" width="16.6666666666667" style="3" customWidth="1"/>
     <col min="45" max="45" width="14.7777777777778" style="3" customWidth="1"/>
     <col min="46" max="47" width="23.7777777777778" style="3" customWidth="1"/>
-    <col min="48" max="16384" width="8.88888888888889" style="3"/>
+    <col min="48" max="48" width="37.7777777777778" customWidth="1"/>
+    <col min="49" max="49" width="27.8888888888889" customWidth="1"/>
+    <col min="50" max="50" width="31.7777777777778" customWidth="1"/>
+    <col min="51" max="51" width="27.8888888888889" customWidth="1"/>
+    <col min="52" max="16384" width="8.88888888888889" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:47">
+    <row r="1" s="1" customFormat="1" spans="1:51">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1644,1006 +1675,1102 @@
       <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="AV1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:47">
-      <c r="A2" s="5" t="s">
-        <v>46</v>
+    <row r="2" s="2" customFormat="1" spans="1:51">
+      <c r="A2" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U2" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y2" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE2" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI2" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN2" s="2">
         <v>73</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS2" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:47">
-      <c r="A3" s="5" t="s">
-        <v>46</v>
+    <row r="3" s="2" customFormat="1" spans="1:51">
+      <c r="A3" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U3" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE3" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG3" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI3" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI3" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN3" s="2">
         <v>73</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS3" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:47">
-      <c r="A4" s="5" t="s">
-        <v>46</v>
+    <row r="4" s="2" customFormat="1" spans="1:51">
+      <c r="A4" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U4" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE4" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG4" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI4" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI4" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM4" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN4" s="2">
         <v>73</v>
       </c>
       <c r="AO4" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS4" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT4" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU4" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:47">
-      <c r="A5" s="5" t="s">
-        <v>46</v>
+    <row r="5" s="2" customFormat="1" spans="1:51">
+      <c r="A5" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N5" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U5" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W5" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y5" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE5" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI5" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI5" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM5" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN5" s="2">
         <v>73</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS5" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT5" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU5" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:47">
-      <c r="A6" s="5" t="s">
-        <v>46</v>
+    <row r="6" s="2" customFormat="1" spans="1:51">
+      <c r="A6" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U6" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE6" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG6" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI6" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI6" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL6" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM6" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN6" s="2">
         <v>73</v>
       </c>
       <c r="AO6" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS6" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT6" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU6" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:47">
-      <c r="A7" s="5" t="s">
-        <v>46</v>
+    <row r="7" s="2" customFormat="1" spans="1:51">
+      <c r="A7" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U7" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE7" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG7" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI7" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI7" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ7" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN7" s="2">
         <v>73</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS7" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT7" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:47">
-      <c r="A8" s="5" t="s">
-        <v>46</v>
+    <row r="8" s="2" customFormat="1" spans="1:51">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="S8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="U8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="W8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AE8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="AG8" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI8" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="AI8" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AN8" s="2">
         <v>73</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AP8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AQ8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="AS8" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AT8" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AU8" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
